--- a/data_orden/data/Localizaciones.corr.xlsx
+++ b/data_orden/data/Localizaciones.corr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Inmuebles Arrendados\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA24BFE2-804E-4B19-A53F-6BAAB4B2BBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD4451E-5B3E-4C79-8FF0-EA5983053B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5400" yWindow="4092" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -76,12 +76,86 @@
         </r>
       </text>
     </comment>
+    <comment ref="A24" authorId="0" shapeId="0" xr:uid="{5FF24EF6-8C82-4608-9ABF-1003E4671958}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ESTADISTICA:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Son el mismo lugar llamado Aldea de Riobamba</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A25" authorId="0" shapeId="0" xr:uid="{D78C3805-862C-408D-B032-329B78B81243}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Son el mismo lugar llamado Aldea de Riobamba
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A30" authorId="0" shapeId="0" xr:uid="{D0CB4A6F-0D22-4F84-9091-2FBBCCDF0FE1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ESTADISTICA:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+A la dirección le falta la letra A luego de la 43
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="43">
   <si>
     <t>address</t>
   </si>
@@ -153,18 +227,122 @@
   </si>
   <si>
     <t>CL 9 SUR 79 A 72</t>
+  </si>
+  <si>
+    <t>CR 81 7 48</t>
+  </si>
+  <si>
+    <t>CR 75 DA 2 B SUR 320</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>CR 39 A 61 B SUR 74</t>
+  </si>
+  <si>
+    <t>Sabaneta</t>
+  </si>
+  <si>
+    <t>CR 35 75 SUR 41</t>
+  </si>
+  <si>
+    <t>CR 43 C 4 SUR 143</t>
+  </si>
+  <si>
+    <t>Poblado</t>
+  </si>
+  <si>
+    <t>CR 48 4 SUR 200</t>
+  </si>
+  <si>
+    <t>CR 42 5 SUR 105</t>
+  </si>
+  <si>
+    <t>CR 45 1 59</t>
+  </si>
+  <si>
+    <t>CL 1 35 388</t>
+  </si>
+  <si>
+    <t>CR 30 2 70</t>
+  </si>
+  <si>
+    <t>CR 37 A 29 72</t>
+  </si>
+  <si>
+    <t>CL 19 43 G 80</t>
+  </si>
+  <si>
+    <r>
+      <t>CR 43</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 32 39</t>
+    </r>
+  </si>
+  <si>
+    <t>CL 5 SUR 25 233</t>
+  </si>
+  <si>
+    <t>CL 28 31 19</t>
+  </si>
+  <si>
+    <r>
+      <t>CL 5 S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 25 233</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0.00000"/>
     <numFmt numFmtId="165" formatCode="#,##0.00000000000000"/>
     <numFmt numFmtId="166" formatCode="#,##0.0000000"/>
+    <numFmt numFmtId="176" formatCode="#,##0.000000000"/>
+    <numFmt numFmtId="177" formatCode="#,##0.0000000000"/>
+    <numFmt numFmtId="178" formatCode="#,##0.00000000000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -191,6 +369,26 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -212,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -220,6 +418,18 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -534,13 +744,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -767,7 +978,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -781,7 +992,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -795,7 +1006,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -807,6 +1018,239 @@
       </c>
       <c r="D19" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20">
+        <v>6.2193486483621996</v>
+      </c>
+      <c r="C20">
+        <v>-75.602517023266003</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="7">
+        <v>6.2055100000000003</v>
+      </c>
+      <c r="C21" s="8">
+        <v>-75.599310000000003</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="9">
+        <v>6.1506690819802801</v>
+      </c>
+      <c r="C22">
+        <v>-75.605539089698993</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23">
+        <v>6.1431049230803803</v>
+      </c>
+      <c r="C23">
+        <v>-75.614027116736594</v>
+      </c>
+      <c r="D23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="10">
+        <v>6.2003656647582499</v>
+      </c>
+      <c r="C24">
+        <v>-75.576072516427004</v>
+      </c>
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25">
+        <v>6.2012206869961499</v>
+      </c>
+      <c r="C25">
+        <v>-75.577266796531006</v>
+      </c>
+      <c r="D25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26">
+        <v>6.1978684312551797</v>
+      </c>
+      <c r="C26">
+        <v>-75.572815065978205</v>
+      </c>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27">
+        <v>6.2054757571363997</v>
+      </c>
+      <c r="C27">
+        <v>-75.575148760836896</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28">
+        <v>6.2029440967304703</v>
+      </c>
+      <c r="C28">
+        <v>-75.569805556183596</v>
+      </c>
+      <c r="D28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29">
+        <v>6.1998339078687801</v>
+      </c>
+      <c r="C29">
+        <v>-75.562710064096905</v>
+      </c>
+      <c r="D29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30">
+        <v>6.2325358425078896</v>
+      </c>
+      <c r="C30">
+        <v>-75.569802118212607</v>
+      </c>
+      <c r="D30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="11">
+        <v>6.2283366361338999</v>
+      </c>
+      <c r="C31">
+        <v>-75.564789821177598</v>
+      </c>
+      <c r="D31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="11">
+        <v>6.2220457226222203</v>
+      </c>
+      <c r="C32">
+        <v>-75.573503565057194</v>
+      </c>
+      <c r="D32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="11">
+        <v>6.1932089660288696</v>
+      </c>
+      <c r="C33">
+        <v>-75.562406723559306</v>
+      </c>
+      <c r="D33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="11">
+        <v>6.2255598265081904</v>
+      </c>
+      <c r="C34">
+        <v>-75.560795728534899</v>
+      </c>
+      <c r="D34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="12">
+        <v>6.1931741895951999</v>
+      </c>
+      <c r="C35">
+        <v>-75.5623997347966</v>
+      </c>
+      <c r="D35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D36" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
